--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/06_Insolvenz_AssetDeal/05_Closing_Checkliste.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/06_Insolvenz_AssetDeal/05_Closing_Checkliste.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing_Items" sheetId="1" r:id="R7d4d525546634249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kunden_Consents" sheetId="2" r:id="R97b6a9d8555b4ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technische_Uebergabe" sheetId="3" r:id="R44caf7420ccf4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closing_Items" sheetId="1" r:id="Rb8c02ff53fd74088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kunden_Consents" sheetId="2" r:id="Re5389d3ea0834d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technische_Uebergabe" sheetId="3" r:id="Rdfeac3f1850247bb"/>
   </x:sheets>
 </x:workbook>
 </file>
